--- a/app/output/report.xlsx
+++ b/app/output/report.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="270">
   <si>
     <t>Анализ рынка организации беговых мероприятий в России, ориентированный на сбыт</t>
   </si>
@@ -493,16 +493,58 @@
     <t>Таблица 3. Валовая рентабельность по годам, %</t>
   </si>
   <si>
+    <t>Таблица 4. Сводные показатели рынка по годам</t>
+  </si>
+  <si>
+    <t>Год</t>
+  </si>
+  <si>
+    <t>Сумма выручки, тыс. руб.</t>
+  </si>
+  <si>
+    <t>Медиана выручки, тыс. руб.</t>
+  </si>
+  <si>
+    <t>Медиана рентабельности, %</t>
+  </si>
+  <si>
+    <t>Распределение показателей по компаниям (boxplot, PNG)</t>
+  </si>
+  <si>
     <t>Таблица 1. Матрица корреляций Спирмена (ρ)</t>
   </si>
   <si>
-    <t>N = 33 полных наблюдений. Значения от −1 до +1.</t>
+    <t>N = 33 полных наблюдений. Цветовая шкала: синий (−1) → белый (0) → красный (+1).</t>
+  </si>
+  <si>
+    <t>Себестоимость</t>
+  </si>
+  <si>
+    <t>Чист. прибыль</t>
+  </si>
+  <si>
+    <t>Активы</t>
+  </si>
+  <si>
+    <t>Ден. средства</t>
+  </si>
+  <si>
+    <t>Кредит. задолж.</t>
+  </si>
+  <si>
+    <t>Вал. рент., %</t>
+  </si>
+  <si>
+    <t>Рент. по ЧП, %</t>
+  </si>
+  <si>
+    <t>Оборач. активов</t>
   </si>
   <si>
     <t>Таблица 2. Статистическая значимость корреляций (p-value)</t>
   </si>
   <si>
-    <t>p &lt; 0.05 — корреляция значима. p &lt; 0.01 — высоко значима.</t>
+    <t>p &lt; 0.05 — значима, p &lt; 0.01 — высоко значима. Зелёный фон — значимые.</t>
   </si>
   <si>
     <t>Формулировка</t>
@@ -541,10 +583,10 @@
     <t>Корреляция между выручкой и рентабельностью по ЧП значима</t>
   </si>
   <si>
-    <t>Доля себестоимости в выручке снижается при росте выручки</t>
-  </si>
-  <si>
-    <t>Положительная корреляция между приростом выручки и приростом КЗ</t>
+    <t>Доля себестоимости снижается при росте выручки</t>
+  </si>
+  <si>
+    <t>Положительная корреляция приростов выручки и КЗ</t>
   </si>
   <si>
     <t>Вилкоксон (односторонний, H₁: медиана &gt; 0)</t>
@@ -568,16 +610,34 @@
     <t>НЕ ПОДТВЕРЖДЕНА</t>
   </si>
   <si>
-    <t>Медиана темпа роста = +33.9%. Положительных наблюдений: 25 из 29 (86%). По годам: 2022: +49%, 2023: +55%, 2024: +32%, 2025: +20%. Темпы замедляются от ~50% к ~20%, что указывает на переход к зрелому росту.</t>
-  </si>
-  <si>
-    <t>Корреляция слабая и незначимая (ρ = -0.080, p = 0.638). Крупнейшая компания (Лига героев, выручка 1.16 млрд) работала в убыток 4 года из 5. Марафон Сервис с меньшей выручкой стабильно прибылен (медиана рент. ~25%). Рентабельность определяется бизнес-моделью, а не масштабом.</t>
-  </si>
-  <si>
-    <t>Направление ожидаемое (отрицательное, ρ = -0.195), но связь незначима (p = 0.254). Затраты на организацию мероприятий (логистика, аренда, персонал) растут примерно пропорционально масштабу. Эффект масштаба в отрасли не выявлен.</t>
-  </si>
-  <si>
-    <t>Положительная тенденция (ρ = 0.324), но незначима (p = 0.114). При расширении выборки связь может стать значимой. Направление экономически логично: быстрорастущие компании финансируют расширение за счёт отсрочки платежей поставщикам.</t>
+    <t>Медиана = +33.9%. Положительных: 25/29 (86%). По годам: 2022: +49%, 2023: +55%, 2024: +32%, 2025: +20%. Темпы замедляются от ~50% к ~20%.</t>
+  </si>
+  <si>
+    <t>ρ = -0.080, p = 0.638. Лига героев (выручка 1.16 млрд) убыточна 4 года из 5. Марафон Сервис с меньшей выручкой — самый прибыльный (медиана рент. ~25%).</t>
+  </si>
+  <si>
+    <t>ρ = -0.195, p = 0.254. Направление ожидаемое (−), но незначимо. Затраты на организацию мероприятий растут пропорционально масштабу.</t>
+  </si>
+  <si>
+    <t>ρ = 0.324, p = 0.114. Тенденция (+), но незначима. При расширении выборки может стать значимой.</t>
+  </si>
+  <si>
+    <t>Данные для графика H2</t>
+  </si>
+  <si>
+    <t>Выручка, тыс. руб.</t>
+  </si>
+  <si>
+    <t>Данные для графика H3</t>
+  </si>
+  <si>
+    <t>Данные для графика H5</t>
+  </si>
+  <si>
+    <t>Темп роста выручки, %</t>
+  </si>
+  <si>
+    <t>Темп роста КЗ, %</t>
   </si>
   <si>
     <t>Регрессионный анализ: Валовая рентабельность, % = a + b · ln(Выручка)</t>
@@ -613,6 +673,21 @@
     <t>Выполнены</t>
   </si>
   <si>
+    <t>Данные для графика</t>
+  </si>
+  <si>
+    <t>ln(Выручка)</t>
+  </si>
+  <si>
+    <t>Вал. рентабельность, %</t>
+  </si>
+  <si>
+    <t>Регрессия (предсказ.), %</t>
+  </si>
+  <si>
+    <t>Диагностика остатков (PNG)</t>
+  </si>
+  <si>
     <t>Кластерный анализ (k-means, k=3, силуэт=0.211)</t>
   </si>
   <si>
@@ -625,6 +700,48 @@
     <t>Таблица 2. Средние значения по кластерам</t>
   </si>
   <si>
+    <t>Выручка, тыс.</t>
+  </si>
+  <si>
+    <t>Оборач., раз</t>
+  </si>
+  <si>
+    <t>Доля КЗ, %</t>
+  </si>
+  <si>
+    <t>Доля ДС, %</t>
+  </si>
+  <si>
+    <t>Кластер 0</t>
+  </si>
+  <si>
+    <t>Кластер 1</t>
+  </si>
+  <si>
+    <t>Кластер 2</t>
+  </si>
+  <si>
+    <t>Таблица 3. Стандартизованный профиль кластеров (z-score)</t>
+  </si>
+  <si>
+    <t>Показатель</t>
+  </si>
+  <si>
+    <t>Вал. рент.</t>
+  </si>
+  <si>
+    <t>Оборач.</t>
+  </si>
+  <si>
+    <t>Доля КЗ</t>
+  </si>
+  <si>
+    <t>Доля ДС</t>
+  </si>
+  <si>
+    <t>Визуализация кластеров (PNG)</t>
+  </si>
+  <si>
     <t>Вердикты по гипотезам</t>
   </si>
   <si>
@@ -637,13 +754,13 @@
     <t>p &lt; 0.0001</t>
   </si>
   <si>
-    <t>Медианный рост +34% г/г. Суммарная выручка ×3.2 за 4 года. Темпы замедляются (50%→20%) — переход к зрелому росту.</t>
+    <t>Медианный рост +34% г/г. Суммарная выручка ×3.2 за 4 года. Темпы замедляются (50%→20%).</t>
   </si>
   <si>
     <t>p = 0.638</t>
   </si>
   <si>
-    <t>ρ = −0.08. Крупнейшая компания (Лига героев) убыточна 4 года из 5. Марафон Сервис с меньшей выручкой — самый прибыльный.</t>
+    <t>ρ = −0.08. Крупнейшая компания убыточна 4 года из 5. Рентабельность определяется бизнес-моделью.</t>
   </si>
   <si>
     <t>p = 0.254</t>
@@ -661,13 +778,13 @@
     <t>силуэт = 0.211</t>
   </si>
   <si>
-    <t>3 содержательных кластера: «малые организаторы», «кэш-генераторы», «лидеры рынка». Слабая статистика из-за малой выборки.</t>
+    <t>3 содержательных кластера: «малые организаторы», «кэш-генераторы», «лидеры рынка».</t>
   </si>
   <si>
     <t>p = 0.114</t>
   </si>
   <si>
-    <t>ρ = +0.32. Экономически логичная тенденция, но незначима. При расширении выборки может стать значимой.</t>
+    <t>ρ = +0.32. Экономически логичная тенденция, но незначима при текущей выборке.</t>
   </si>
   <si>
     <t>Качественные выводы о рынке</t>
@@ -679,25 +796,25 @@
     <t>2. Прибыльность не связана с масштабом — определяется бизнес-моделью и управлением затратами</t>
   </si>
   <si>
-    <t>3. Две модели финансирования: предоплаты от участников (высокая ликвидность) vs кредиторская задолженность поставщикам</t>
-  </si>
-  <si>
-    <t>4. Себестоимость — ключевой фактор: медианная доля 89%, маржа ~10%, крайне чувствительна к управлению затратами</t>
-  </si>
-  <si>
-    <t>5. Бизнес low-asset: компании с минимальными основными средствами показывают наибольшие темпы роста</t>
+    <t>3. Две модели финансирования: предоплаты от участников (высокая ликвидность) vs КЗ поставщикам</t>
+  </si>
+  <si>
+    <t>4. Себестоимость — ключевой фактор: медианная доля 89%, маржа ~10%</t>
+  </si>
+  <si>
+    <t>5. Бизнес low-asset: компании с минимальными ОС показывают наибольшие темпы роста</t>
   </si>
   <si>
     <t>Рекомендации для ЛПР</t>
   </si>
   <si>
-    <t>Для организаторов: контролировать себестоимость (маржа ~10%), использовать модель предоплат, не гнаться за масштабом ради масштаба</t>
-  </si>
-  <si>
-    <t>Для инвесторов: рынок растущий (+34% г/г), входной барьер низкий (low-asset), дифференциация важнее размера</t>
-  </si>
-  <si>
-    <t>Для регуляторов: рынок прозрачен через ГИРБО, желательна стандартизация отчётности НКО для сопоставимости</t>
+    <t>Для организаторов: контролировать себестоимость (маржа ~10%), использовать модель предоплат</t>
+  </si>
+  <si>
+    <t>Для инвесторов: рынок растущий (+34% г/г), входной барьер низкий (low-asset)</t>
+  </si>
+  <si>
+    <t>Для регуляторов: рынок прозрачен через ГИРБО, стандартизировать отчётность НКО</t>
   </si>
   <si>
     <t>Ограничения исследования</t>
@@ -706,16 +823,16 @@
     <t>1. Малая выборка (11 компаний, 49 наблюдений) — ограничивает мощность статистических тестов</t>
   </si>
   <si>
-    <t>2. Только финансовые данные — нет операционных метрик (число участников, мероприятий, средний чек)</t>
-  </si>
-  <si>
-    <t>3. Разнородность ОПФ (ООО vs НКО) — ограничивает сопоставимость отдельных показателей</t>
-  </si>
-  <si>
-    <t>4. Юрлицо ≠ бренд — одна компания может работать через несколько юрлиц</t>
-  </si>
-  <si>
-    <t>5. Факторный анализ не проведён из-за недостаточного числа наблюдений для устойчивого выделения факторов</t>
+    <t>2. Только финансовые данные — нет операционных метрик (число участников, мероприятий)</t>
+  </si>
+  <si>
+    <t>3. Разнородность ОПФ (ООО vs НКО) — ограничивает сопоставимость</t>
+  </si>
+  <si>
+    <t>4. Юрлицо ≠ бренд — возможны связанные юрлица</t>
+  </si>
+  <si>
+    <t>5. Факторный анализ не проведён из-за малого числа наблюдений</t>
   </si>
 </sst>
 </file>
@@ -847,9 +964,4366 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="167" formatCode="0.0000"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Динамика выручки по компаниям, тыс. руб.</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Динамика рынка'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>АНО "ЛИГА ГЕРОЕВ"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$2:$F$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$3:$F$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>382870</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>592044</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>722644</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>967665</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1164006</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Динамика рынка'!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>АНО "ПАРКРАН"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$2:$F$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$4:$F$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>829</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2310</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9174</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12702</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12521</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Динамика рынка'!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>АССОЦИАЦИЯ "ПЕТЕРБУРГСКИЙ СПОРТ"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$2:$F$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$5:$F$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="1">
+                  <c:v>30327</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Динамика рынка'!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ООО "АРЕНА ПЛЮС"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$2:$F$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$6:$F$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>98226</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>213877</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>240124</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>241307</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>266403</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Динамика рынка'!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ООО "АРХИТЕКТУРА СПОРТА"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$2:$F$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$7:$F$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>240322</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>276106</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>321461</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>381088</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>364529</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Динамика рынка'!$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ООО "АСМ "НОВЫЙ СПОРТ"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$2:$F$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$8:$F$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>40436</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>52757</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>84481</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>167019</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>229304</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Динамика рынка'!$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ООО "ГРУТ"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$2:$F$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$9:$F$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>51542</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>85441</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>165536</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>218094</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>392726</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Динамика рынка'!$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ООО "МАРАФОН СЕРВИС"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$2:$F$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$10:$F$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>122541</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>175036</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>272143</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>235895</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>553024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Динамика рынка'!$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ООО "ЯРОСЛАВСКОЕ БЕГОВОЕ СООБЩЕСТВО"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$2:$F$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$11:$F$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:marker val="1"/>
+        <c:axId val="50010001"/>
+        <c:axId val="50010002"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="50010001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Год</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50010002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50010002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" vert="horz"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>тыс. руб.</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50010001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="800" baseline="0"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Профиль кластеров (стандартизованные значения)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Кластерный анализ'!$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Кластер 0</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4C72B0"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Кластерный анализ'!$A$23:$A$27</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Выручка</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Вал. рент.</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Оборач.</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Доля КЗ</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Доля ДС</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Кластерный анализ'!$B$23:$B$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-0.7067015031701356</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.6259365449639627</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.01607557287385498</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.6555053524555666</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.5491746355588045</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Кластерный анализ'!$C$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Кластер 1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="DD8452"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Кластерный анализ'!$A$23:$A$27</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Выручка</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Вал. рент.</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Оборач.</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Доля КЗ</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Доля ДС</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Кластерный анализ'!$C$23:$C$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.005907037821025037</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.194104481838694</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.4181187748202648</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.6398242179002801</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.706942053208546</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Кластерный анализ'!$D$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Кластер 2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="55A868"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Кластерный анализ'!$A$23:$A$27</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Выручка</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Вал. рент.</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Оборач.</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Доля КЗ</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Доля ДС</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Кластерный анализ'!$D$23:$D$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.407495968519246</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.057768608089231</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.4502699205679753</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.6711864870108524</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.608592782090937</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="50100001"/>
+        <c:axId val="50100002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="50100001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50100002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50100002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>z-score</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50100001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Динамика чистой прибыли, тыс. руб.</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Динамика рынка'!$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>АНО "ЛИГА ГЕРОЕВ"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$14:$F$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$15:$F$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-19162</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-186806</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-57838</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-57506</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>53312</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Динамика рынка'!$A$16</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>АНО "ПАРКРАН"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$14:$F$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$16:$F$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-89</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>351</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>116</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2635</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>899</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Динамика рынка'!$A$17</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>АССОЦИАЦИЯ "ПЕТЕРБУРГСКИЙ СПОРТ"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$14:$F$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$17:$F$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="1">
+                  <c:v>3068</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Динамика рынка'!$A$18</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ООО "АРЕНА ПЛЮС"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$14:$F$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$18:$F$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-6187</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17978</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2554</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9861</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3956</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Динамика рынка'!$A$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ООО "АРХИТЕКТУРА СПОРТА"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$14:$F$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$19:$F$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>26548</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>35472</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>53385</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>69831</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20467</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Динамика рынка'!$A$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ООО "АСМ "НОВЫЙ СПОРТ"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$14:$F$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$20:$F$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>3838</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4768</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7607</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>53735</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17371</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Динамика рынка'!$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ООО "ГРУТ"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$14:$F$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$21:$F$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-6704</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-2933</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-11677</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Динамика рынка'!$A$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ООО "МАРАФОН СЕРВИС"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$14:$F$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$22:$F$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>30207</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>40021</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45725</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20114</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>82203</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Динамика рынка'!$A$23</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ООО "ЯРОСЛАВСКОЕ БЕГОВОЕ СООБЩЕСТВО"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$14:$F$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$23:$F$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:marker val="1"/>
+        <c:axId val="50020001"/>
+        <c:axId val="50020002"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="50020001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Год</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50020002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50020002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" vert="horz"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>тыс. руб.</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50020001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="800" baseline="0"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Динамика валовой рентабельности, %</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Динамика рынка'!$A$27</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>АНО "ЛИГА ГЕРОЕВ"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$26:$F$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$27:$F$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>44.10452634053334</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-15.28062103492308</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.208235313653749</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-1.653051417587698</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10.64934373190516</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Динамика рынка'!$A$28</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>АНО "ПАРКРАН"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$26:$F$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$28:$F$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-2.533172496984319</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14.71861471861472</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.235011990407674</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>23.3034167847583</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.192955834198546</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Динамика рынка'!$A$29</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>АССОЦИАЦИЯ "ПЕТЕРБУРГСКИЙ СПОРТ"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$26:$F$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$29:$F$29</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="1">
+                  <c:v>1.44755498400765</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Динамика рынка'!$A$30</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ООО "АРЕНА ПЛЮС"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$26:$F$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$30:$F$30</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-3.159041394335512</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12.37486966808025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.100081624494011</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.223105836134053</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.415866187693082</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Динамика рынка'!$A$31</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ООО "АРХИТЕКТУРА СПОРТА"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$26:$F$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$31:$F$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>18.66828671532361</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>19.02964803372618</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>29.74793209751727</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>22.47040053740868</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.498053652795799</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Динамика рынка'!$A$32</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ООО "АСМ "НОВЫЙ СПОРТ"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$26:$F$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$32:$F$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>10.54505885844297</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10.04226927232405</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10.28752027083013</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>34.83196522551327</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11.49347590970938</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Динамика рынка'!$A$33</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ООО "ГРУТ"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$26:$F$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$33:$F$33</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-9.303092623491521</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.944722088926861</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.3606466267156389</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15.64508881491467</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15.73208802065562</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Динамика рынка'!$A$34</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ООО "МАРАФОН СЕРВИС"</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$26:$F$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$34:$F$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>31.27851086575105</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30.85822345117576</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>24.94240160503853</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16.39415841794019</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>21.59219129730355</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:marker val="1"/>
+        <c:axId val="50030001"/>
+        <c:axId val="50030002"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="50030001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Год</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50030002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50030002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" vert="horz"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>%</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50030001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="800" baseline="0"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Суммарная выручка рынка, тыс. руб.</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4C72B0"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$A$122:$A$126</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$B$122:$B$126</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>936809</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1427898</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1815563</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2223770</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2982513</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="50040001"/>
+        <c:axId val="50040002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="50040001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Год</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50040002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50040002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>тыс. руб.</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50040001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Медианная выручка, тыс. руб.</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="31750">
+              <a:solidFill>
+                <a:srgbClr val="DD8452"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="DD8452"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$A$122:$A$126</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Динамика рынка'!$C$122:$C$126</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>74884</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>85441</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>240124</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>235895</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>364529</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:marker val="1"/>
+        <c:axId val="50050001"/>
+        <c:axId val="50050002"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="50050001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Год</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50050002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50050002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" vert="horz"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>тыс. руб.</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50050001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>H2: Масштаб vs Рентабельность (ρ=-0.08, p=0.638)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="4C72B0"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Проверка гипотез'!$A$11:$A$47</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="37"/>
+                <c:pt idx="0">
+                  <c:v>382870</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>592044</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>722644</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>967665</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1164006</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>829</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2310</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9174</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>12702</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>12521</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>30327</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>98226</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>213877</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>240124</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>241307</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>266403</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>240322</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>276106</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>321461</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>381088</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>364529</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>40436</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>52757</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>84481</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>167019</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>229304</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>51542</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>85441</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>165536</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>218094</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>392726</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>122541</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>175036</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>272143</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>235895</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>553024</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>43</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Проверка гипотез'!$B$11:$B$47</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="37"/>
+                <c:pt idx="0">
+                  <c:v>-5.004831927286024</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-31.55272243279216</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-8.003664321574663</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-5.94275911601639</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.580045120042336</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-10.73582629674307</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15.19480519480519</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.264442991061696</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20.74476460399937</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7.179937704656178</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10.11639792923797</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-6.298739641235517</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>8.405765930885508</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.063617131148906</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.086495625903932</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.484968262369418</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>11.04684548231123</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>12.84723982818193</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>16.60699120577613</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>18.32411411537493</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5.614642456430078</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>9.491542190127609</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>9.037663248478875</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>9.004391519986743</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>32.17298630694712</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7.575532917001011</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-13.00686818516938</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-3.432778174412753</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-7.054054707133192</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.03897402037653489</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.0002546304548209184</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>24.65052513036453</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>22.86443931534085</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>16.80182845048375</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>8.526675003709277</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>14.86427352158315</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:axId val="50060001"/>
+        <c:axId val="50060002"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="50060001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Выручка, тыс. руб.</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50060002"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="50060002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" vert="horz"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Рентабельность по ЧП, %</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50060001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>H3: Масштаб vs Себестоимость (ρ=-0.20, p=0.254)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="DD8452"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Проверка гипотез'!$D$11:$D$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="36"/>
+                <c:pt idx="0">
+                  <c:v>382870</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>592044</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>722644</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>967665</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1164006</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>829</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2310</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9174</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>12702</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>12521</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>30327</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>98226</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>213877</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>240124</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>241307</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>266403</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>240322</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>276106</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>321461</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>381088</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>364529</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>40436</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>52757</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>84481</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>167019</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>229304</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>51542</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>85441</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>165536</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>218094</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>392726</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>122541</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>175036</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>272143</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>235895</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>553024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Проверка гипотез'!$E$11:$E$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="36"/>
+                <c:pt idx="0">
+                  <c:v>55.89547365946665</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>115.2806210349231</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>94.79176468634624</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>101.6530514175877</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>89.35065626809484</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>102.5331724969843</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>85.28138528138528</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>93.76498800959233</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>76.6965832152417</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>95.80704416580146</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>98.55244501599235</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>103.1590413943355</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>87.62513033191975</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>92.89991837550599</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>90.77689416386595</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>95.58413381230692</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>81.33171328467638</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>80.97035196627382</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>70.25206790248274</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>77.52959946259132</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>94.5019463472042</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>89.45494114155703</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>89.95773072767594</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>89.71247972916987</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>65.16803477448674</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>88.50652409029061</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>109.3030926234915</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>97.05527791107313</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>100.3606466267156</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>84.35491118508534</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>84.26791197934438</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>68.72148913424894</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>69.14177654882424</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>75.05759839496147</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>83.60584158205981</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>78.40780870269644</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:axId val="50070001"/>
+        <c:axId val="50070002"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="50070001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Выручка, тыс. руб.</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50070002"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="50070002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" vert="horz"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Доля себестоимости, %</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50070001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>H5: Рост выручки vs Рост КЗ (ρ=0.32, p=0.114)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="55A868"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Проверка гипотез'!$G$11:$G$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>54.63316530415023</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22.05917127781043</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>33.90618340427651</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20.29018306955404</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-1.424972445284212</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>117.7397023191416</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12.27200680765113</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.4926621245689766</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10.40002983750989</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>14.89002255307463</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>16.4266622239285</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>18.54875085935774</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-4.34519061214208</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>30.47037293500841</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>60.13230471785735</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>97.70007457298091</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>37.29216436453338</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>65.76966357533662</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>93.74305076017369</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>31.7501933114247</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>80.07189560464754</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>42.83872336605707</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>55.47830160652665</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-13.31946807377004</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>134.4365077682868</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Проверка гипотез'!$H$11:$H$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>119.9197951831796</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>77.56681021160861</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-8.643107039458798</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>75.00317540962784</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.41747572815533</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>37.33576552370153</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>80.19851740168362</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-46.61334342689803</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>40.64220012314122</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-24.14437733678458</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>21.99052132701422</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-9.48082220809493</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>68.6378250148266</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>55.90551181102362</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>891.9191919191919</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1540.885947046843</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-61.00474757191174</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>68.11490125673249</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>115.2178556172576</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-47.6256636729023</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>100.2321174798674</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-0.7052387310888419</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-2.100714164479778</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.754587645364337</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>19.62829090389944</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:axId val="50080001"/>
+        <c:axId val="50080002"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="50080001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Темп роста выручки, %</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50080002"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="50080002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" vert="horz"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Темп роста КЗ, %</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50080001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Регрессия: рентабельность от масштаба (R²=0.031, p=0.301)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Наблюдения</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="4C72B0"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Регрессия!$A$15:$A$50</c:f>
+              <c:strCache>
+                <c:ptCount val="36"/>
+                <c:pt idx="0">
+                  <c:v>6.720220155135295</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.745002803515839</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.124128675157117</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.435162513668947</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.44951474036292</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10.31979368382217</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>10.60747575627395</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10.85015228826527</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10.87345174395606</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11.34428193599124</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11.35558135824538</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11.4950262250824</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>11.71620094684697</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>12.01694397280324</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>12.02586285738239</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>12.07274694603508</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>12.27315636240735</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>12.29268144149494</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>12.34280391308983</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>12.37114206974935</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>12.38891073556453</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>12.38973496976029</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>12.39382526072406</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>12.49276547884623</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Диагностика остатков (PNG)</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>12.52854012893892</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>12.68063150892524</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>12.80636138830856</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>12.85078559856772</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>12.85545078495741</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>12.88086744667593</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>13.22315667920107</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>13.29133623542855</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>13.49067198706801</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>13.78264123198099</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>13.96737806189941</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Регрессия!$B$15:$B$50</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="36"/>
+                <c:pt idx="0">
+                  <c:v>-2.533172496984319</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14.71861471861472</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.235011990407674</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.192955834198546</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>23.3034167847583</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.44755498400765</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>10.54505885844297</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-9.303092623491521</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10.04226927232405</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10.28752027083013</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.944722088926861</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-3.159041394335512</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>31.27851086575105</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-0.3606466267156389</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>34.83196522551327</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>30.85822345117576</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>12.37486966808025</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>15.64508881491467</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>11.49347590970938</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>16.39415841794019</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>7.100081624494011</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>18.66828671532361</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>9.223105836134053</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4.415866187693082</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>24.94240160503853</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>19.02964803372618</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>29.74793209751727</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>5.498053652795799</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>22.47040053740868</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>44.10452634053334</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>15.73208802065562</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>21.59219129730355</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>-15.28062103492308</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>5.208235313653749</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-1.653051417587698</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>10.64934373190516</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>y = -4.2 + 1.40·x</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Регрессия!$A$15:$A$50</c:f>
+              <c:strCache>
+                <c:ptCount val="36"/>
+                <c:pt idx="0">
+                  <c:v>6.720220155135295</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.745002803515839</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.124128675157117</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.435162513668947</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.44951474036292</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10.31979368382217</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>10.60747575627395</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10.85015228826527</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10.87345174395606</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11.34428193599124</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11.35558135824538</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11.4950262250824</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>11.71620094684697</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>12.01694397280324</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>12.02586285738239</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>12.07274694603508</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>12.27315636240735</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>12.29268144149494</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>12.34280391308983</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>12.37114206974935</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>12.38891073556453</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>12.38973496976029</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>12.39382526072406</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>12.49276547884623</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Диагностика остатков (PNG)</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>12.52854012893892</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>12.68063150892524</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>12.80636138830856</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>12.85078559856772</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>12.85545078495741</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>12.88086744667593</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>13.22315667920107</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>13.29133623542855</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>13.49067198706801</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>13.78264123198099</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>13.96737806189941</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Регрессия!$C$15:$C$50</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="36"/>
+                <c:pt idx="0">
+                  <c:v>5.24308054794338</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.680483620306436</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.614903341605636</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.051172433195251</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.071303467593392</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10.29199317103251</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>10.69550809730437</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11.03589636717406</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>11.06857715977653</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11.72898331093664</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11.74483235394072</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11.94042356572942</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12.25065249583069</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>12.67248726263168</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>12.68499726376839</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>12.7507588505603</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>13.03186149342727</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>13.05924818729156</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>13.12955206565912</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>13.16930035131937</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>13.19422342634888</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>13.19537953176032</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>13.20111674521477</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>13.33989443991307</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>13.36979520734609</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>13.390073462789</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>13.60340320370309</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>13.77975719954701</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>13.84206845785601</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>13.84861204371813</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>13.88426251818815</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>14.36437173475807</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>14.46000323647075</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>14.73959991220599</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>15.14912820616828</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>15.40824782272597</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:axId val="50090001"/>
+        <c:axId val="50090002"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="50090001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>ln(Выручка)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50090002"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="50090002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" vert="horz"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Валовая рентабельность, %</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50090001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -858,14 +5332,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>150</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>93728</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>96902</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>591944</xdr:colOff>
+      <xdr:row>196</xdr:row>
+      <xdr:rowOff>139227</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -882,8 +5356,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="7239000"/>
-          <a:ext cx="12352403" cy="8669402"/>
+          <a:off x="0" y="28575000"/>
+          <a:ext cx="11631419" cy="8902227"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -892,42 +5366,154 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>529693</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>189883</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="14478000"/>
-          <a:ext cx="11569168" cy="3999883"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>127</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>144</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>127</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>144</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -935,18 +5521,113 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1238250</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1238250</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>398665</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>64132</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>388796</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>160085</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -963,8 +5644,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="6286500"/>
-          <a:ext cx="6437515" cy="5779132"/>
+          <a:off x="0" y="7429500"/>
+          <a:ext cx="8161196" cy="3017585"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -973,23 +5654,53 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1081736</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>135491</xdr:rowOff>
+      <xdr:colOff>767172</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>119434</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1006,8 +5717,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="1524000"/>
-          <a:ext cx="13083236" cy="4135991"/>
+          <a:off x="0" y="8953500"/>
+          <a:ext cx="10168347" cy="4310434"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1016,90 +5727,34 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>130965</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>145096</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="2095500"/>
-          <a:ext cx="13094490" cy="3764596"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>16665</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>131513</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="3810000"/>
-          <a:ext cx="13094490" cy="4513013"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1690,7 +6345,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="45.7109375" customWidth="1"/>
@@ -1701,7 +6356,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="6" t="s">
-        <v>200</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1709,163 +6364,163 @@
         <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>201</v>
+        <v>240</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>202</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>203</v>
+        <v>242</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>204</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>205</v>
+        <v>244</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>206</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>207</v>
+        <v>246</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>209</v>
+        <v>248</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>210</v>
+        <v>249</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>211</v>
+        <v>250</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>212</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="3" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>213</v>
+        <v>252</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>214</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="6" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="3" t="s">
-        <v>216</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="3" t="s">
-        <v>217</v>
+        <v>256</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="3" t="s">
-        <v>218</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="3" t="s">
-        <v>219</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="3" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="6" t="s">
-        <v>221</v>
+        <v>259</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="3" t="s">
-        <v>222</v>
+      <c r="A18" s="6" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="3" t="s">
-        <v>223</v>
+        <v>261</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="6" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="3" t="s">
-        <v>226</v>
+        <v>262</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="3" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="3" t="s">
-        <v>227</v>
+      <c r="A24" s="6" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="3" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="3" t="s">
-        <v>229</v>
+        <v>266</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="3" t="s">
-        <v>230</v>
+        <v>267</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="3" t="s">
+        <v>269</v>
       </c>
     </row>
   </sheetData>
@@ -6846,7 +11501,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F150"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
@@ -6859,27 +11514,27 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="2">
         <v>2021</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <v>2022</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="2">
         <v>2023</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="2">
         <v>2024</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <v>2025</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
         <v>103</v>
       </c>
       <c r="B3" s="4">
@@ -6899,7 +11554,7 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
         <v>104</v>
       </c>
       <c r="B4" s="4">
@@ -6919,7 +11574,7 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" t="s">
+      <c r="A5" s="3" t="s">
         <v>107</v>
       </c>
       <c r="C5" s="4">
@@ -6927,7 +11582,7 @@
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" t="s">
+      <c r="A6" s="3" t="s">
         <v>108</v>
       </c>
       <c r="B6" s="4">
@@ -6947,7 +11602,7 @@
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" t="s">
+      <c r="A7" s="3" t="s">
         <v>109</v>
       </c>
       <c r="B7" s="4">
@@ -6967,7 +11622,7 @@
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" t="s">
+      <c r="A8" s="3" t="s">
         <v>110</v>
       </c>
       <c r="B8" s="4">
@@ -6987,7 +11642,7 @@
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" t="s">
+      <c r="A9" s="3" t="s">
         <v>111</v>
       </c>
       <c r="B9" s="4">
@@ -7007,7 +11662,7 @@
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" t="s">
+      <c r="A10" s="3" t="s">
         <v>112</v>
       </c>
       <c r="B10" s="4">
@@ -7027,7 +11682,7 @@
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" t="s">
+      <c r="A11" s="3" t="s">
         <v>113</v>
       </c>
       <c r="B11" s="4">
@@ -7037,358 +11692,452 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>154</v>
+      </c>
+    </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
-        <v>154</v>
+      <c r="A14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="2">
+        <v>2021</v>
+      </c>
+      <c r="C14" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D14" s="2">
+        <v>2023</v>
+      </c>
+      <c r="E14" s="2">
+        <v>2024</v>
+      </c>
+      <c r="F14" s="2">
+        <v>2025</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" t="s">
+      <c r="A15" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B15" s="4">
+        <v>-19162</v>
+      </c>
+      <c r="C15" s="4">
+        <v>-186806</v>
+      </c>
+      <c r="D15" s="4">
+        <v>-57838</v>
+      </c>
+      <c r="E15" s="4">
+        <v>-57506</v>
+      </c>
+      <c r="F15" s="4">
+        <v>53312</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="4">
+        <v>-89</v>
+      </c>
+      <c r="C16" s="4">
+        <v>351</v>
+      </c>
+      <c r="D16" s="4">
+        <v>116</v>
+      </c>
+      <c r="E16" s="4">
+        <v>2635</v>
+      </c>
+      <c r="F16" s="4">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C17" s="4">
+        <v>3068</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" s="4">
+        <v>-6187</v>
+      </c>
+      <c r="C18" s="4">
+        <v>17978</v>
+      </c>
+      <c r="D18" s="4">
+        <v>2554</v>
+      </c>
+      <c r="E18" s="4">
+        <v>9861</v>
+      </c>
+      <c r="F18" s="4">
+        <v>3956</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" s="4">
+        <v>26548</v>
+      </c>
+      <c r="C19" s="4">
+        <v>35472</v>
+      </c>
+      <c r="D19" s="4">
+        <v>53385</v>
+      </c>
+      <c r="E19" s="4">
+        <v>69831</v>
+      </c>
+      <c r="F19" s="4">
+        <v>20467</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" s="4">
+        <v>3838</v>
+      </c>
+      <c r="C20" s="4">
+        <v>4768</v>
+      </c>
+      <c r="D20" s="4">
+        <v>7607</v>
+      </c>
+      <c r="E20" s="4">
+        <v>53735</v>
+      </c>
+      <c r="F20" s="4">
+        <v>17371</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B21" s="4">
+        <v>-6704</v>
+      </c>
+      <c r="C21" s="4">
+        <v>-2933</v>
+      </c>
+      <c r="D21" s="4">
+        <v>-11677</v>
+      </c>
+      <c r="E21" s="4">
+        <v>85</v>
+      </c>
+      <c r="F21" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B22" s="4">
+        <v>30207</v>
+      </c>
+      <c r="C22" s="4">
+        <v>40021</v>
+      </c>
+      <c r="D22" s="4">
+        <v>45725</v>
+      </c>
+      <c r="E22" s="4">
+        <v>20114</v>
+      </c>
+      <c r="F22" s="4">
+        <v>82203</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B23" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B15">
+      <c r="B26" s="2">
         <v>2021</v>
       </c>
-      <c r="C15">
+      <c r="C26" s="2">
         <v>2022</v>
       </c>
-      <c r="D15">
+      <c r="D26" s="2">
         <v>2023</v>
       </c>
-      <c r="E15">
+      <c r="E26" s="2">
         <v>2024</v>
       </c>
-      <c r="F15">
+      <c r="F26" s="2">
         <v>2025</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
-      <c r="A16" t="s">
+    <row r="27" spans="1:6">
+      <c r="A27" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B16" s="4">
-        <v>-19162</v>
-      </c>
-      <c r="C16" s="4">
-        <v>-186806</v>
-      </c>
-      <c r="D16" s="4">
-        <v>-57838</v>
-      </c>
-      <c r="E16" s="4">
-        <v>-57506</v>
-      </c>
-      <c r="F16" s="4">
-        <v>53312</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" t="s">
+      <c r="B27" s="5">
+        <v>44.10452634053334</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-15.28062103492308</v>
+      </c>
+      <c r="D27" s="5">
+        <v>5.208235313653749</v>
+      </c>
+      <c r="E27" s="5">
+        <v>-1.653051417587698</v>
+      </c>
+      <c r="F27" s="5">
+        <v>10.64934373190516</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="4">
-        <v>-89</v>
-      </c>
-      <c r="C17" s="4">
-        <v>351</v>
-      </c>
-      <c r="D17" s="4">
-        <v>116</v>
-      </c>
-      <c r="E17" s="4">
-        <v>2635</v>
-      </c>
-      <c r="F17" s="4">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" t="s">
+      <c r="B28" s="5">
+        <v>-2.533172496984319</v>
+      </c>
+      <c r="C28" s="5">
+        <v>14.71861471861472</v>
+      </c>
+      <c r="D28" s="5">
+        <v>6.235011990407674</v>
+      </c>
+      <c r="E28" s="5">
+        <v>23.3034167847583</v>
+      </c>
+      <c r="F28" s="5">
+        <v>4.192955834198546</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C18" s="4">
-        <v>3068</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" t="s">
+      <c r="C29" s="5">
+        <v>1.44755498400765</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B19" s="4">
-        <v>-6187</v>
-      </c>
-      <c r="C19" s="4">
-        <v>17978</v>
-      </c>
-      <c r="D19" s="4">
-        <v>2554</v>
-      </c>
-      <c r="E19" s="4">
-        <v>9861</v>
-      </c>
-      <c r="F19" s="4">
-        <v>3956</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" t="s">
+      <c r="B30" s="5">
+        <v>-3.159041394335512</v>
+      </c>
+      <c r="C30" s="5">
+        <v>12.37486966808025</v>
+      </c>
+      <c r="D30" s="5">
+        <v>7.100081624494011</v>
+      </c>
+      <c r="E30" s="5">
+        <v>9.223105836134053</v>
+      </c>
+      <c r="F30" s="5">
+        <v>4.415866187693082</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B20" s="4">
-        <v>26548</v>
-      </c>
-      <c r="C20" s="4">
-        <v>35472</v>
-      </c>
-      <c r="D20" s="4">
-        <v>53385</v>
-      </c>
-      <c r="E20" s="4">
-        <v>69831</v>
-      </c>
-      <c r="F20" s="4">
-        <v>20467</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" t="s">
+      <c r="B31" s="5">
+        <v>18.66828671532361</v>
+      </c>
+      <c r="C31" s="5">
+        <v>19.02964803372618</v>
+      </c>
+      <c r="D31" s="5">
+        <v>29.74793209751727</v>
+      </c>
+      <c r="E31" s="5">
+        <v>22.47040053740868</v>
+      </c>
+      <c r="F31" s="5">
+        <v>5.498053652795799</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B21" s="4">
-        <v>3838</v>
-      </c>
-      <c r="C21" s="4">
-        <v>4768</v>
-      </c>
-      <c r="D21" s="4">
-        <v>7607</v>
-      </c>
-      <c r="E21" s="4">
-        <v>53735</v>
-      </c>
-      <c r="F21" s="4">
-        <v>17371</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" t="s">
+      <c r="B32" s="5">
+        <v>10.54505885844297</v>
+      </c>
+      <c r="C32" s="5">
+        <v>10.04226927232405</v>
+      </c>
+      <c r="D32" s="5">
+        <v>10.28752027083013</v>
+      </c>
+      <c r="E32" s="5">
+        <v>34.83196522551327</v>
+      </c>
+      <c r="F32" s="5">
+        <v>11.49347590970938</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B22" s="4">
-        <v>-6704</v>
-      </c>
-      <c r="C22" s="4">
-        <v>-2933</v>
-      </c>
-      <c r="D22" s="4">
-        <v>-11677</v>
-      </c>
-      <c r="E22" s="4">
-        <v>85</v>
-      </c>
-      <c r="F22" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" t="s">
+      <c r="B33" s="5">
+        <v>-9.303092623491521</v>
+      </c>
+      <c r="C33" s="5">
+        <v>2.944722088926861</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-0.3606466267156389</v>
+      </c>
+      <c r="E33" s="5">
+        <v>15.64508881491467</v>
+      </c>
+      <c r="F33" s="5">
+        <v>15.73208802065562</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B23" s="4">
-        <v>30207</v>
-      </c>
-      <c r="C23" s="4">
-        <v>40021</v>
-      </c>
-      <c r="D23" s="4">
-        <v>45725</v>
-      </c>
-      <c r="E23" s="4">
-        <v>20114</v>
-      </c>
-      <c r="F23" s="4">
-        <v>82203</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" t="s">
-        <v>113</v>
-      </c>
-      <c r="B24" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="6" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" t="s">
-        <v>71</v>
-      </c>
-      <c r="B28">
+      <c r="B34" s="5">
+        <v>31.27851086575105</v>
+      </c>
+      <c r="C34" s="5">
+        <v>30.85822345117576</v>
+      </c>
+      <c r="D34" s="5">
+        <v>24.94240160503853</v>
+      </c>
+      <c r="E34" s="5">
+        <v>16.39415841794019</v>
+      </c>
+      <c r="F34" s="5">
+        <v>21.59219129730355</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" s="6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" s="3">
         <v>2021</v>
       </c>
-      <c r="C28">
+      <c r="B122" s="4">
+        <v>936809</v>
+      </c>
+      <c r="C122" s="4">
+        <v>74884</v>
+      </c>
+      <c r="D122" s="5">
+        <v>10.54505885844297</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" s="3">
         <v>2022</v>
       </c>
-      <c r="D28">
+      <c r="B123" s="4">
+        <v>1427898</v>
+      </c>
+      <c r="C123" s="4">
+        <v>85441</v>
+      </c>
+      <c r="D123" s="5">
+        <v>11.20856947020215</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" s="3">
         <v>2023</v>
       </c>
-      <c r="E28">
+      <c r="B124" s="4">
+        <v>1815563</v>
+      </c>
+      <c r="C124" s="4">
+        <v>240124</v>
+      </c>
+      <c r="D124" s="5">
+        <v>7.100081624494011</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" s="3">
         <v>2024</v>
       </c>
-      <c r="F28">
+      <c r="B125" s="4">
+        <v>2223770</v>
+      </c>
+      <c r="C125" s="4">
+        <v>235895</v>
+      </c>
+      <c r="D125" s="5">
+        <v>16.39415841794019</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" s="3">
         <v>2025</v>
       </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" t="s">
-        <v>103</v>
-      </c>
-      <c r="B29" s="5">
-        <v>44.10452634053334</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-15.28062103492308</v>
-      </c>
-      <c r="D29" s="5">
-        <v>5.208235313653749</v>
-      </c>
-      <c r="E29" s="5">
-        <v>-1.653051417587698</v>
-      </c>
-      <c r="F29" s="5">
+      <c r="B126" s="4">
+        <v>2982513</v>
+      </c>
+      <c r="C126" s="4">
+        <v>364529</v>
+      </c>
+      <c r="D126" s="5">
         <v>10.64934373190516</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
-      <c r="A30" t="s">
-        <v>104</v>
-      </c>
-      <c r="B30" s="5">
-        <v>-2.533172496984319</v>
-      </c>
-      <c r="C30" s="5">
-        <v>14.71861471861472</v>
-      </c>
-      <c r="D30" s="5">
-        <v>6.235011990407674</v>
-      </c>
-      <c r="E30" s="5">
-        <v>23.3034167847583</v>
-      </c>
-      <c r="F30" s="5">
-        <v>4.192955834198546</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" t="s">
-        <v>107</v>
-      </c>
-      <c r="C31" s="5">
-        <v>1.44755498400765</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" t="s">
-        <v>108</v>
-      </c>
-      <c r="B32" s="5">
-        <v>-3.159041394335512</v>
-      </c>
-      <c r="C32" s="5">
-        <v>12.37486966808025</v>
-      </c>
-      <c r="D32" s="5">
-        <v>7.100081624494011</v>
-      </c>
-      <c r="E32" s="5">
-        <v>9.223105836134053</v>
-      </c>
-      <c r="F32" s="5">
-        <v>4.415866187693082</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" t="s">
-        <v>109</v>
-      </c>
-      <c r="B33" s="5">
-        <v>18.66828671532361</v>
-      </c>
-      <c r="C33" s="5">
-        <v>19.02964803372618</v>
-      </c>
-      <c r="D33" s="5">
-        <v>29.74793209751727</v>
-      </c>
-      <c r="E33" s="5">
-        <v>22.47040053740868</v>
-      </c>
-      <c r="F33" s="5">
-        <v>5.498053652795799</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" t="s">
-        <v>110</v>
-      </c>
-      <c r="B34" s="5">
-        <v>10.54505885844297</v>
-      </c>
-      <c r="C34" s="5">
-        <v>10.04226927232405</v>
-      </c>
-      <c r="D34" s="5">
-        <v>10.28752027083013</v>
-      </c>
-      <c r="E34" s="5">
-        <v>34.83196522551327</v>
-      </c>
-      <c r="F34" s="5">
-        <v>11.49347590970938</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" t="s">
-        <v>111</v>
-      </c>
-      <c r="B35" s="5">
-        <v>-9.303092623491521</v>
-      </c>
-      <c r="C35" s="5">
-        <v>2.944722088926861</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-0.3606466267156389</v>
-      </c>
-      <c r="E35" s="5">
-        <v>15.64508881491467</v>
-      </c>
-      <c r="F35" s="5">
-        <v>15.73208802065562</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" t="s">
-        <v>112</v>
-      </c>
-      <c r="B36" s="5">
-        <v>31.27851086575105</v>
-      </c>
-      <c r="C36" s="5">
-        <v>30.85822345117576</v>
-      </c>
-      <c r="D36" s="5">
-        <v>24.94240160503853</v>
-      </c>
-      <c r="E36" s="5">
-        <v>16.39415841794019</v>
-      </c>
-      <c r="F36" s="5">
-        <v>21.59219129730355</v>
+    <row r="150" spans="1:1">
+      <c r="A150" s="7" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -7403,49 +12152,51 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
+    <col min="2" max="10" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="6" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="7" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="B3" t="s">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F3" t="s">
-        <v>79</v>
-      </c>
-      <c r="G3" t="s">
-        <v>88</v>
-      </c>
-      <c r="H3" t="s">
-        <v>115</v>
-      </c>
-      <c r="I3" t="s">
-        <v>116</v>
-      </c>
-      <c r="J3" t="s">
-        <v>123</v>
+      <c r="C3" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
         <v>90</v>
       </c>
       <c r="B4" s="8">
@@ -7477,8 +12228,8 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>91</v>
+      <c r="A5" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="B5" s="8">
         <v>0.9786096256684492</v>
@@ -7509,8 +12260,8 @@
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>102</v>
+      <c r="A6" s="3" t="s">
+        <v>165</v>
       </c>
       <c r="B6" s="8">
         <v>0.1149732620320856</v>
@@ -7541,8 +12292,8 @@
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>81</v>
+      <c r="A7" s="3" t="s">
+        <v>166</v>
       </c>
       <c r="B7" s="8">
         <v>0.8439171122994652</v>
@@ -7573,8 +12324,8 @@
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>79</v>
+      <c r="A8" s="3" t="s">
+        <v>167</v>
       </c>
       <c r="B8" s="8">
         <v>0.7443181818181818</v>
@@ -7605,8 +12356,8 @@
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" t="s">
-        <v>88</v>
+      <c r="A9" s="3" t="s">
+        <v>168</v>
       </c>
       <c r="B9" s="8">
         <v>0.7697192513368984</v>
@@ -7637,8 +12388,8 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" t="s">
-        <v>115</v>
+      <c r="A10" s="3" t="s">
+        <v>169</v>
       </c>
       <c r="B10" s="8">
         <v>0.1356951871657754</v>
@@ -7669,8 +12420,8 @@
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" t="s">
-        <v>116</v>
+      <c r="A11" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="B11" s="8">
         <v>-0.2182486631016043</v>
@@ -7701,8 +12452,8 @@
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" t="s">
-        <v>123</v>
+      <c r="A12" s="3" t="s">
+        <v>171</v>
       </c>
       <c r="B12" s="8">
         <v>-0.3465909090909091</v>
@@ -7734,45 +12485,46 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="6" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="7" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="B17" t="s">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C17" t="s">
-        <v>91</v>
-      </c>
-      <c r="D17" t="s">
-        <v>102</v>
-      </c>
-      <c r="E17" t="s">
-        <v>81</v>
-      </c>
-      <c r="F17" t="s">
-        <v>79</v>
-      </c>
-      <c r="G17" t="s">
-        <v>88</v>
-      </c>
-      <c r="H17" t="s">
-        <v>115</v>
-      </c>
-      <c r="I17" t="s">
-        <v>116</v>
-      </c>
-      <c r="J17" t="s">
-        <v>123</v>
+      <c r="C17" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" t="s">
+      <c r="A18" s="3" t="s">
         <v>90</v>
       </c>
       <c r="B18" s="9">
@@ -7804,8 +12556,8 @@
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" t="s">
-        <v>91</v>
+      <c r="A19" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="B19" s="9">
         <v>7.615053178208727E-27</v>
@@ -7836,8 +12588,8 @@
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" t="s">
-        <v>102</v>
+      <c r="A20" s="3" t="s">
+        <v>165</v>
       </c>
       <c r="B20" s="9">
         <v>0.2489214099746236</v>
@@ -7868,8 +12620,8 @@
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" t="s">
-        <v>81</v>
+      <c r="A21" s="3" t="s">
+        <v>166</v>
       </c>
       <c r="B21" s="9">
         <v>6.241227696657421E-14</v>
@@ -7900,8 +12652,8 @@
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" t="s">
-        <v>79</v>
+      <c r="A22" s="3" t="s">
+        <v>167</v>
       </c>
       <c r="B22" s="9">
         <v>1.137784341163278E-09</v>
@@ -7932,8 +12684,8 @@
       </c>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" t="s">
-        <v>88</v>
+      <c r="A23" s="3" t="s">
+        <v>168</v>
       </c>
       <c r="B23" s="9">
         <v>1.641676736165625E-07</v>
@@ -7964,8 +12716,8 @@
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" t="s">
-        <v>115</v>
+      <c r="A24" s="3" t="s">
+        <v>169</v>
       </c>
       <c r="B24" s="9">
         <v>0.2535051266973358</v>
@@ -7996,8 +12748,8 @@
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" t="s">
-        <v>116</v>
+      <c r="A25" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="B25" s="9">
         <v>0.6383129562096617</v>
@@ -8028,8 +12780,8 @@
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" t="s">
-        <v>123</v>
+      <c r="A26" s="3" t="s">
+        <v>171</v>
       </c>
       <c r="B26" s="9">
         <v>0.1014936718137329</v>
@@ -8060,14 +12812,30 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B18:J26">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+      <formula>0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4:J12">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="-1"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FF2166AC"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FFB2182B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8084,59 +12852,59 @@
         <v>10</v>
       </c>
       <c r="B1" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="C1" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="D1" t="s">
         <v>131</v>
       </c>
       <c r="E1" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="F1" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="G1" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="H1" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="B2" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="C2" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="D2">
         <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="F2">
         <v>9E-06</v>
       </c>
       <c r="G2" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="H2" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="B3" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="C3" t="s">
         <v>17</v>
@@ -8145,24 +12913,24 @@
         <v>37</v>
       </c>
       <c r="E3" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="F3">
         <v>0.638313</v>
       </c>
       <c r="G3" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="H3" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="B4" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
@@ -8171,24 +12939,24 @@
         <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="F4">
         <v>0.253505</v>
       </c>
       <c r="G4" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="H4" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="B5" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -8197,16 +12965,709 @@
         <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="F5">
         <v>0.114283</v>
       </c>
       <c r="G5" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="H5" t="s">
-        <v>184</v>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="4">
+        <v>382870</v>
+      </c>
+      <c r="B11" s="5">
+        <v>-5.004831927286024</v>
+      </c>
+      <c r="D11" s="4">
+        <v>382870</v>
+      </c>
+      <c r="E11" s="5">
+        <v>55.89547365946665</v>
+      </c>
+      <c r="G11" s="5">
+        <v>54.63316530415023</v>
+      </c>
+      <c r="H11" s="5">
+        <v>119.9197951831796</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="4">
+        <v>592044</v>
+      </c>
+      <c r="B12" s="5">
+        <v>-31.55272243279216</v>
+      </c>
+      <c r="D12" s="4">
+        <v>592044</v>
+      </c>
+      <c r="E12" s="5">
+        <v>115.2806210349231</v>
+      </c>
+      <c r="G12" s="5">
+        <v>22.05917127781043</v>
+      </c>
+      <c r="H12" s="5">
+        <v>77.56681021160861</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="4">
+        <v>722644</v>
+      </c>
+      <c r="B13" s="5">
+        <v>-8.003664321574663</v>
+      </c>
+      <c r="D13" s="4">
+        <v>722644</v>
+      </c>
+      <c r="E13" s="5">
+        <v>94.79176468634624</v>
+      </c>
+      <c r="G13" s="5">
+        <v>33.90618340427651</v>
+      </c>
+      <c r="H13" s="5">
+        <v>-8.643107039458798</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="4">
+        <v>967665</v>
+      </c>
+      <c r="B14" s="5">
+        <v>-5.94275911601639</v>
+      </c>
+      <c r="D14" s="4">
+        <v>967665</v>
+      </c>
+      <c r="E14" s="5">
+        <v>101.6530514175877</v>
+      </c>
+      <c r="G14" s="5">
+        <v>20.29018306955404</v>
+      </c>
+      <c r="H14" s="5">
+        <v>75.00317540962784</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="4">
+        <v>1164006</v>
+      </c>
+      <c r="B15" s="5">
+        <v>4.580045120042336</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1164006</v>
+      </c>
+      <c r="E15" s="5">
+        <v>89.35065626809484</v>
+      </c>
+      <c r="G15" s="5">
+        <v>-1.424972445284212</v>
+      </c>
+      <c r="H15" s="5">
+        <v>19.41747572815533</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="4">
+        <v>829</v>
+      </c>
+      <c r="B16" s="5">
+        <v>-10.73582629674307</v>
+      </c>
+      <c r="D16" s="4">
+        <v>829</v>
+      </c>
+      <c r="E16" s="5">
+        <v>102.5331724969843</v>
+      </c>
+      <c r="G16" s="5">
+        <v>117.7397023191416</v>
+      </c>
+      <c r="H16" s="5">
+        <v>37.33576552370153</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="4">
+        <v>2310</v>
+      </c>
+      <c r="B17" s="5">
+        <v>15.19480519480519</v>
+      </c>
+      <c r="D17" s="4">
+        <v>2310</v>
+      </c>
+      <c r="E17" s="5">
+        <v>85.28138528138528</v>
+      </c>
+      <c r="G17" s="5">
+        <v>12.27200680765113</v>
+      </c>
+      <c r="H17" s="5">
+        <v>80.19851740168362</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="4">
+        <v>9174</v>
+      </c>
+      <c r="B18" s="5">
+        <v>1.264442991061696</v>
+      </c>
+      <c r="D18" s="4">
+        <v>9174</v>
+      </c>
+      <c r="E18" s="5">
+        <v>93.76498800959233</v>
+      </c>
+      <c r="G18" s="5">
+        <v>0.4926621245689766</v>
+      </c>
+      <c r="H18" s="5">
+        <v>-46.61334342689803</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="4">
+        <v>12702</v>
+      </c>
+      <c r="B19" s="5">
+        <v>20.74476460399937</v>
+      </c>
+      <c r="D19" s="4">
+        <v>12702</v>
+      </c>
+      <c r="E19" s="5">
+        <v>76.6965832152417</v>
+      </c>
+      <c r="G19" s="5">
+        <v>10.40002983750989</v>
+      </c>
+      <c r="H19" s="5">
+        <v>40.64220012314122</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="4">
+        <v>12521</v>
+      </c>
+      <c r="B20" s="5">
+        <v>7.179937704656178</v>
+      </c>
+      <c r="D20" s="4">
+        <v>12521</v>
+      </c>
+      <c r="E20" s="5">
+        <v>95.80704416580146</v>
+      </c>
+      <c r="G20" s="5">
+        <v>14.89002255307463</v>
+      </c>
+      <c r="H20" s="5">
+        <v>-24.14437733678458</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="4">
+        <v>30327</v>
+      </c>
+      <c r="B21" s="5">
+        <v>10.11639792923797</v>
+      </c>
+      <c r="D21" s="4">
+        <v>30327</v>
+      </c>
+      <c r="E21" s="5">
+        <v>98.55244501599235</v>
+      </c>
+      <c r="G21" s="5">
+        <v>16.4266622239285</v>
+      </c>
+      <c r="H21" s="5">
+        <v>21.99052132701422</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="4">
+        <v>98226</v>
+      </c>
+      <c r="B22" s="5">
+        <v>-6.298739641235517</v>
+      </c>
+      <c r="D22" s="4">
+        <v>98226</v>
+      </c>
+      <c r="E22" s="5">
+        <v>103.1590413943355</v>
+      </c>
+      <c r="G22" s="5">
+        <v>18.54875085935774</v>
+      </c>
+      <c r="H22" s="5">
+        <v>-9.48082220809493</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="4">
+        <v>213877</v>
+      </c>
+      <c r="B23" s="5">
+        <v>8.405765930885508</v>
+      </c>
+      <c r="D23" s="4">
+        <v>213877</v>
+      </c>
+      <c r="E23" s="5">
+        <v>87.62513033191975</v>
+      </c>
+      <c r="G23" s="5">
+        <v>-4.34519061214208</v>
+      </c>
+      <c r="H23" s="5">
+        <v>68.6378250148266</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="4">
+        <v>240124</v>
+      </c>
+      <c r="B24" s="5">
+        <v>1.063617131148906</v>
+      </c>
+      <c r="D24" s="4">
+        <v>240124</v>
+      </c>
+      <c r="E24" s="5">
+        <v>92.89991837550599</v>
+      </c>
+      <c r="G24" s="5">
+        <v>30.47037293500841</v>
+      </c>
+      <c r="H24" s="5">
+        <v>55.90551181102362</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="4">
+        <v>241307</v>
+      </c>
+      <c r="B25" s="5">
+        <v>4.086495625903932</v>
+      </c>
+      <c r="D25" s="4">
+        <v>241307</v>
+      </c>
+      <c r="E25" s="5">
+        <v>90.77689416386595</v>
+      </c>
+      <c r="G25" s="5">
+        <v>60.13230471785735</v>
+      </c>
+      <c r="H25" s="5">
+        <v>891.9191919191919</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="4">
+        <v>266403</v>
+      </c>
+      <c r="B26" s="5">
+        <v>1.484968262369418</v>
+      </c>
+      <c r="D26" s="4">
+        <v>266403</v>
+      </c>
+      <c r="E26" s="5">
+        <v>95.58413381230692</v>
+      </c>
+      <c r="G26" s="5">
+        <v>97.70007457298091</v>
+      </c>
+      <c r="H26" s="5">
+        <v>1540.885947046843</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="4">
+        <v>240322</v>
+      </c>
+      <c r="B27" s="5">
+        <v>11.04684548231123</v>
+      </c>
+      <c r="D27" s="4">
+        <v>240322</v>
+      </c>
+      <c r="E27" s="5">
+        <v>81.33171328467638</v>
+      </c>
+      <c r="G27" s="5">
+        <v>37.29216436453338</v>
+      </c>
+      <c r="H27" s="5">
+        <v>-61.00474757191174</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="4">
+        <v>276106</v>
+      </c>
+      <c r="B28" s="5">
+        <v>12.84723982818193</v>
+      </c>
+      <c r="D28" s="4">
+        <v>276106</v>
+      </c>
+      <c r="E28" s="5">
+        <v>80.97035196627382</v>
+      </c>
+      <c r="G28" s="5">
+        <v>65.76966357533662</v>
+      </c>
+      <c r="H28" s="5">
+        <v>68.11490125673249</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="4">
+        <v>321461</v>
+      </c>
+      <c r="B29" s="5">
+        <v>16.60699120577613</v>
+      </c>
+      <c r="D29" s="4">
+        <v>321461</v>
+      </c>
+      <c r="E29" s="5">
+        <v>70.25206790248274</v>
+      </c>
+      <c r="G29" s="5">
+        <v>93.74305076017369</v>
+      </c>
+      <c r="H29" s="5">
+        <v>115.2178556172576</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="4">
+        <v>381088</v>
+      </c>
+      <c r="B30" s="5">
+        <v>18.32411411537493</v>
+      </c>
+      <c r="D30" s="4">
+        <v>381088</v>
+      </c>
+      <c r="E30" s="5">
+        <v>77.52959946259132</v>
+      </c>
+      <c r="G30" s="5">
+        <v>31.7501933114247</v>
+      </c>
+      <c r="H30" s="5">
+        <v>-47.6256636729023</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="4">
+        <v>364529</v>
+      </c>
+      <c r="B31" s="5">
+        <v>5.614642456430078</v>
+      </c>
+      <c r="D31" s="4">
+        <v>364529</v>
+      </c>
+      <c r="E31" s="5">
+        <v>94.5019463472042</v>
+      </c>
+      <c r="G31" s="5">
+        <v>80.07189560464754</v>
+      </c>
+      <c r="H31" s="5">
+        <v>100.2321174798674</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="4">
+        <v>40436</v>
+      </c>
+      <c r="B32" s="5">
+        <v>9.491542190127609</v>
+      </c>
+      <c r="D32" s="4">
+        <v>40436</v>
+      </c>
+      <c r="E32" s="5">
+        <v>89.45494114155703</v>
+      </c>
+      <c r="G32" s="5">
+        <v>42.83872336605707</v>
+      </c>
+      <c r="H32" s="5">
+        <v>-0.7052387310888419</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="4">
+        <v>52757</v>
+      </c>
+      <c r="B33" s="5">
+        <v>9.037663248478875</v>
+      </c>
+      <c r="D33" s="4">
+        <v>52757</v>
+      </c>
+      <c r="E33" s="5">
+        <v>89.95773072767594</v>
+      </c>
+      <c r="G33" s="5">
+        <v>55.47830160652665</v>
+      </c>
+      <c r="H33" s="5">
+        <v>-2.100714164479778</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="4">
+        <v>84481</v>
+      </c>
+      <c r="B34" s="5">
+        <v>9.004391519986743</v>
+      </c>
+      <c r="D34" s="4">
+        <v>84481</v>
+      </c>
+      <c r="E34" s="5">
+        <v>89.71247972916987</v>
+      </c>
+      <c r="G34" s="5">
+        <v>-13.31946807377004</v>
+      </c>
+      <c r="H34" s="5">
+        <v>2.754587645364337</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="4">
+        <v>167019</v>
+      </c>
+      <c r="B35" s="5">
+        <v>32.17298630694712</v>
+      </c>
+      <c r="D35" s="4">
+        <v>167019</v>
+      </c>
+      <c r="E35" s="5">
+        <v>65.16803477448674</v>
+      </c>
+      <c r="G35" s="5">
+        <v>134.4365077682868</v>
+      </c>
+      <c r="H35" s="5">
+        <v>19.62829090389944</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="4">
+        <v>229304</v>
+      </c>
+      <c r="B36" s="5">
+        <v>7.575532917001011</v>
+      </c>
+      <c r="D36" s="4">
+        <v>229304</v>
+      </c>
+      <c r="E36" s="5">
+        <v>88.50652409029061</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="4">
+        <v>51542</v>
+      </c>
+      <c r="B37" s="5">
+        <v>-13.00686818516938</v>
+      </c>
+      <c r="D37" s="4">
+        <v>51542</v>
+      </c>
+      <c r="E37" s="5">
+        <v>109.3030926234915</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="4">
+        <v>85441</v>
+      </c>
+      <c r="B38" s="5">
+        <v>-3.432778174412753</v>
+      </c>
+      <c r="D38" s="4">
+        <v>85441</v>
+      </c>
+      <c r="E38" s="5">
+        <v>97.05527791107313</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="4">
+        <v>165536</v>
+      </c>
+      <c r="B39" s="5">
+        <v>-7.054054707133192</v>
+      </c>
+      <c r="D39" s="4">
+        <v>165536</v>
+      </c>
+      <c r="E39" s="5">
+        <v>100.3606466267156</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="4">
+        <v>218094</v>
+      </c>
+      <c r="B40" s="5">
+        <v>0.03897402037653489</v>
+      </c>
+      <c r="D40" s="4">
+        <v>218094</v>
+      </c>
+      <c r="E40" s="5">
+        <v>84.35491118508534</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="4">
+        <v>392726</v>
+      </c>
+      <c r="B41" s="5">
+        <v>0.0002546304548209184</v>
+      </c>
+      <c r="D41" s="4">
+        <v>392726</v>
+      </c>
+      <c r="E41" s="5">
+        <v>84.26791197934438</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="4">
+        <v>122541</v>
+      </c>
+      <c r="B42" s="5">
+        <v>24.65052513036453</v>
+      </c>
+      <c r="D42" s="4">
+        <v>122541</v>
+      </c>
+      <c r="E42" s="5">
+        <v>68.72148913424894</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="4">
+        <v>175036</v>
+      </c>
+      <c r="B43" s="5">
+        <v>22.86443931534085</v>
+      </c>
+      <c r="D43" s="4">
+        <v>175036</v>
+      </c>
+      <c r="E43" s="5">
+        <v>69.14177654882424</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="4">
+        <v>272143</v>
+      </c>
+      <c r="B44" s="5">
+        <v>16.80182845048375</v>
+      </c>
+      <c r="D44" s="4">
+        <v>272143</v>
+      </c>
+      <c r="E44" s="5">
+        <v>75.05759839496147</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="4">
+        <v>235895</v>
+      </c>
+      <c r="B45" s="5">
+        <v>8.526675003709277</v>
+      </c>
+      <c r="D45" s="4">
+        <v>235895</v>
+      </c>
+      <c r="E45" s="5">
+        <v>83.60584158205981</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="4">
+        <v>553024</v>
+      </c>
+      <c r="B46" s="5">
+        <v>14.86427352158315</v>
+      </c>
+      <c r="D46" s="4">
+        <v>553024</v>
+      </c>
+      <c r="E46" s="5">
+        <v>78.40780870269644</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="4">
+        <v>43</v>
+      </c>
+      <c r="B47" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8217,67 +13678,68 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="45.7109375" customWidth="1"/>
     <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" s="6" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="B3" s="9">
         <v>-4.183</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:3">
       <c r="A4" s="3" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="B4" s="9">
         <v>1.4026</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:3">
       <c r="A5" s="3" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="B5" s="9">
         <v>1.3343</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:3">
       <c r="A6" s="3" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="B6" s="9">
         <v>0.0315</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:3">
       <c r="A7" s="3" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="B7" s="9">
         <v>0.300565</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:3">
       <c r="A8" s="3" t="s">
         <v>131</v>
       </c>
@@ -8285,20 +13747,432 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:3">
       <c r="A9" s="3" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="B9" s="9">
         <v>0.9706</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:3">
       <c r="A10" s="3" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>195</v>
+        <v>215</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="7" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="8">
+        <v>6.720220155135295</v>
+      </c>
+      <c r="B15" s="5">
+        <v>-2.533172496984319</v>
+      </c>
+      <c r="C15" s="5">
+        <v>5.24308054794338</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="8">
+        <v>7.745002803515839</v>
+      </c>
+      <c r="B16" s="5">
+        <v>14.71861471861472</v>
+      </c>
+      <c r="C16" s="5">
+        <v>6.680483620306436</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="8">
+        <v>9.124128675157117</v>
+      </c>
+      <c r="B17" s="5">
+        <v>6.235011990407674</v>
+      </c>
+      <c r="C17" s="5">
+        <v>8.614903341605636</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="8">
+        <v>9.435162513668947</v>
+      </c>
+      <c r="B18" s="5">
+        <v>4.192955834198546</v>
+      </c>
+      <c r="C18" s="5">
+        <v>9.051172433195251</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="8">
+        <v>9.44951474036292</v>
+      </c>
+      <c r="B19" s="5">
+        <v>23.3034167847583</v>
+      </c>
+      <c r="C19" s="5">
+        <v>9.071303467593392</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="8">
+        <v>10.31979368382217</v>
+      </c>
+      <c r="B20" s="5">
+        <v>1.44755498400765</v>
+      </c>
+      <c r="C20" s="5">
+        <v>10.29199317103251</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="8">
+        <v>10.60747575627395</v>
+      </c>
+      <c r="B21" s="5">
+        <v>10.54505885844297</v>
+      </c>
+      <c r="C21" s="5">
+        <v>10.69550809730437</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="8">
+        <v>10.85015228826527</v>
+      </c>
+      <c r="B22" s="5">
+        <v>-9.303092623491521</v>
+      </c>
+      <c r="C22" s="5">
+        <v>11.03589636717406</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="8">
+        <v>10.87345174395606</v>
+      </c>
+      <c r="B23" s="5">
+        <v>10.04226927232405</v>
+      </c>
+      <c r="C23" s="5">
+        <v>11.06857715977653</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="8">
+        <v>11.34428193599124</v>
+      </c>
+      <c r="B24" s="5">
+        <v>10.28752027083013</v>
+      </c>
+      <c r="C24" s="5">
+        <v>11.72898331093664</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="8">
+        <v>11.35558135824538</v>
+      </c>
+      <c r="B25" s="5">
+        <v>2.944722088926861</v>
+      </c>
+      <c r="C25" s="5">
+        <v>11.74483235394072</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="8">
+        <v>11.4950262250824</v>
+      </c>
+      <c r="B26" s="5">
+        <v>-3.159041394335512</v>
+      </c>
+      <c r="C26" s="5">
+        <v>11.94042356572942</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="8">
+        <v>11.71620094684697</v>
+      </c>
+      <c r="B27" s="5">
+        <v>31.27851086575105</v>
+      </c>
+      <c r="C27" s="5">
+        <v>12.25065249583069</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="8">
+        <v>12.01694397280324</v>
+      </c>
+      <c r="B28" s="5">
+        <v>-0.3606466267156389</v>
+      </c>
+      <c r="C28" s="5">
+        <v>12.67248726263168</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="8">
+        <v>12.02586285738239</v>
+      </c>
+      <c r="B29" s="5">
+        <v>34.83196522551327</v>
+      </c>
+      <c r="C29" s="5">
+        <v>12.68499726376839</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="8">
+        <v>12.07274694603508</v>
+      </c>
+      <c r="B30" s="5">
+        <v>30.85822345117576</v>
+      </c>
+      <c r="C30" s="5">
+        <v>12.7507588505603</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="8">
+        <v>12.27315636240735</v>
+      </c>
+      <c r="B31" s="5">
+        <v>12.37486966808025</v>
+      </c>
+      <c r="C31" s="5">
+        <v>13.03186149342727</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="8">
+        <v>12.29268144149494</v>
+      </c>
+      <c r="B32" s="5">
+        <v>15.64508881491467</v>
+      </c>
+      <c r="C32" s="5">
+        <v>13.05924818729156</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="8">
+        <v>12.34280391308983</v>
+      </c>
+      <c r="B33" s="5">
+        <v>11.49347590970938</v>
+      </c>
+      <c r="C33" s="5">
+        <v>13.12955206565912</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="8">
+        <v>12.37114206974935</v>
+      </c>
+      <c r="B34" s="5">
+        <v>16.39415841794019</v>
+      </c>
+      <c r="C34" s="5">
+        <v>13.16930035131937</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="8">
+        <v>12.38891073556453</v>
+      </c>
+      <c r="B35" s="5">
+        <v>7.100081624494011</v>
+      </c>
+      <c r="C35" s="5">
+        <v>13.19422342634888</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="8">
+        <v>12.38973496976029</v>
+      </c>
+      <c r="B36" s="5">
+        <v>18.66828671532361</v>
+      </c>
+      <c r="C36" s="5">
+        <v>13.19537953176032</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="8">
+        <v>12.39382526072406</v>
+      </c>
+      <c r="B37" s="5">
+        <v>9.223105836134053</v>
+      </c>
+      <c r="C37" s="5">
+        <v>13.20111674521477</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="8">
+        <v>12.49276547884623</v>
+      </c>
+      <c r="B38" s="5">
+        <v>4.415866187693082</v>
+      </c>
+      <c r="C38" s="5">
+        <v>13.33989443991307</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B39" s="5">
+        <v>24.94240160503853</v>
+      </c>
+      <c r="C39" s="5">
+        <v>13.36979520734609</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="8">
+        <v>12.52854012893892</v>
+      </c>
+      <c r="B40" s="5">
+        <v>19.02964803372618</v>
+      </c>
+      <c r="C40" s="5">
+        <v>13.390073462789</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="8">
+        <v>12.68063150892524</v>
+      </c>
+      <c r="B41" s="5">
+        <v>29.74793209751727</v>
+      </c>
+      <c r="C41" s="5">
+        <v>13.60340320370309</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="8">
+        <v>12.80636138830856</v>
+      </c>
+      <c r="B42" s="5">
+        <v>5.498053652795799</v>
+      </c>
+      <c r="C42" s="5">
+        <v>13.77975719954701</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="8">
+        <v>12.85078559856772</v>
+      </c>
+      <c r="B43" s="5">
+        <v>22.47040053740868</v>
+      </c>
+      <c r="C43" s="5">
+        <v>13.84206845785601</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="8">
+        <v>12.85545078495741</v>
+      </c>
+      <c r="B44" s="5">
+        <v>44.10452634053334</v>
+      </c>
+      <c r="C44" s="5">
+        <v>13.84861204371813</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="8">
+        <v>12.88086744667593</v>
+      </c>
+      <c r="B45" s="5">
+        <v>15.73208802065562</v>
+      </c>
+      <c r="C45" s="5">
+        <v>13.88426251818815</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="8">
+        <v>13.22315667920107</v>
+      </c>
+      <c r="B46" s="5">
+        <v>21.59219129730355</v>
+      </c>
+      <c r="C46" s="5">
+        <v>14.36437173475807</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="8">
+        <v>13.29133623542855</v>
+      </c>
+      <c r="B47" s="5">
+        <v>-15.28062103492308</v>
+      </c>
+      <c r="C47" s="5">
+        <v>14.46000323647075</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="8">
+        <v>13.49067198706801</v>
+      </c>
+      <c r="B48" s="5">
+        <v>5.208235313653749</v>
+      </c>
+      <c r="C48" s="5">
+        <v>14.73959991220599</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="8">
+        <v>13.78264123198099</v>
+      </c>
+      <c r="B49" s="5">
+        <v>-1.653051417587698</v>
+      </c>
+      <c r="C49" s="5">
+        <v>15.14912820616828</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="8">
+        <v>13.96737806189941</v>
+      </c>
+      <c r="B50" s="5">
+        <v>10.64934373190516</v>
+      </c>
+      <c r="C50" s="5">
+        <v>15.40824782272597</v>
       </c>
     </row>
   </sheetData>
@@ -8309,50 +14183,51 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
+    <col min="2" max="8" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="6" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="7" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="2" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
       <c r="C4" s="4">
@@ -8372,10 +14247,10 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" t="s">
+      <c r="A5" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="4">
@@ -8395,10 +14270,10 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" t="s">
+      <c r="A6" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="4">
@@ -8418,10 +14293,10 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" t="s">
+      <c r="A7" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="4">
@@ -8441,10 +14316,10 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" t="s">
+      <c r="A8" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="3">
         <v>1</v>
       </c>
       <c r="C8" s="4">
@@ -8464,10 +14339,10 @@
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" t="s">
+      <c r="A9" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="3">
         <v>0</v>
       </c>
       <c r="C9" s="4">
@@ -8487,10 +14362,10 @@
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" t="s">
+      <c r="A10" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="3">
         <v>1</v>
       </c>
       <c r="C10" s="4">
@@ -8510,10 +14385,10 @@
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" t="s">
+      <c r="A11" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="3">
         <v>2</v>
       </c>
       <c r="C11" s="4">
@@ -8534,32 +14409,32 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="7" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" t="s">
-        <v>198</v>
-      </c>
-      <c r="B15" t="s">
-        <v>90</v>
-      </c>
-      <c r="C15" t="s">
-        <v>115</v>
-      </c>
-      <c r="D15" t="s">
-        <v>123</v>
-      </c>
-      <c r="E15" t="s">
-        <v>121</v>
-      </c>
-      <c r="F15" t="s">
-        <v>119</v>
+      <c r="A15" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16">
-        <v>0</v>
+      <c r="A16" s="3" t="s">
+        <v>229</v>
       </c>
       <c r="B16" s="4">
         <v>134638.75</v>
@@ -8578,8 +14453,8 @@
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17">
-        <v>1</v>
+      <c r="A17" s="3" t="s">
+        <v>230</v>
       </c>
       <c r="B17" s="4">
         <v>378627.5</v>
@@ -8598,8 +14473,8 @@
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18">
-        <v>2</v>
+      <c r="A18" s="3" t="s">
+        <v>231</v>
       </c>
       <c r="B18" s="4">
         <v>858515</v>
@@ -8615,6 +14490,100 @@
       </c>
       <c r="F18" s="5">
         <v>5.053905668735689</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="7" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" s="8">
+        <v>-0.7067015031701356</v>
+      </c>
+      <c r="C23" s="8">
+        <v>0.005907037821025037</v>
+      </c>
+      <c r="D23" s="8">
+        <v>1.407495968519246</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B24" s="8">
+        <v>-0.6259365449639627</v>
+      </c>
+      <c r="C24" s="8">
+        <v>0.194104481838694</v>
+      </c>
+      <c r="D24" s="8">
+        <v>1.057768608089231</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B25" s="8">
+        <v>0.01607557287385498</v>
+      </c>
+      <c r="C25" s="8">
+        <v>0.4181187748202648</v>
+      </c>
+      <c r="D25" s="8">
+        <v>-0.4502699205679753</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B26" s="8">
+        <v>-0.6555053524555666</v>
+      </c>
+      <c r="C26" s="8">
+        <v>0.6398242179002801</v>
+      </c>
+      <c r="D26" s="8">
+        <v>0.6711864870108524</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B27" s="8">
+        <v>-0.5491746355588045</v>
+      </c>
+      <c r="C27" s="8">
+        <v>1.706942053208546</v>
+      </c>
+      <c r="D27" s="8">
+        <v>-0.608592782090937</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="7" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>
